--- a/documents/engineering.xlsx
+++ b/documents/engineering.xlsx
@@ -516,7 +516,6 @@
           <t>2022-03-11</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
         <v>100000</v>
       </c>
@@ -568,7 +567,6 @@
           <t>2024-08-27</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
         <v>117400</v>
       </c>
@@ -620,7 +618,6 @@
           <t>2019-06-26</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
         <v>112500</v>
       </c>
@@ -672,7 +669,6 @@
           <t>2023-08-26</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
         <v>82200</v>
       </c>
@@ -724,7 +720,6 @@
           <t>2024-01-21</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
         <v>91200</v>
       </c>
@@ -776,7 +771,6 @@
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
         <v>98700</v>
       </c>
@@ -828,7 +822,6 @@
           <t>2023-12-25</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
         <v>93500</v>
       </c>
@@ -880,7 +873,6 @@
           <t>2023-05-21</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
         <v>120800</v>
       </c>
@@ -932,7 +924,6 @@
           <t>2025-01-09</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
         <v>140300</v>
       </c>
@@ -984,7 +975,6 @@
           <t>2021-09-20</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
         <v>103300</v>
       </c>
@@ -1036,7 +1026,6 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
         <v>110200</v>
       </c>
@@ -1088,7 +1077,6 @@
           <t>2018-03-14</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
         <v>199600</v>
       </c>
@@ -1140,7 +1128,6 @@
           <t>2021-04-08</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
         <v>115900</v>
       </c>
@@ -1192,7 +1179,6 @@
           <t>2022-12-15</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
         <v>137600</v>
       </c>
@@ -1244,7 +1230,6 @@
           <t>2024-05-25</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
         <v>115700</v>
       </c>
@@ -1296,7 +1281,6 @@
           <t>2019-09-25</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
         <v>133700</v>
       </c>
@@ -1348,7 +1332,6 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
         <v>117600</v>
       </c>
@@ -1400,7 +1383,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
         <v>115300</v>
       </c>
@@ -1452,7 +1434,6 @@
           <t>2020-03-11</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
         <v>105500</v>
       </c>
@@ -1504,7 +1485,6 @@
           <t>2021-12-08</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
         <v>120000</v>
       </c>
@@ -1556,7 +1536,6 @@
           <t>2025-01-10</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
         <v>121300</v>
       </c>
@@ -1608,7 +1587,6 @@
           <t>2023-09-05</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
         <v>112800</v>
       </c>
@@ -1660,7 +1638,6 @@
           <t>2019-08-20</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
         <v>128500</v>
       </c>
@@ -1712,7 +1689,6 @@
           <t>2024-08-10</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
         <v>114600</v>
       </c>
@@ -1764,7 +1740,6 @@
           <t>2018-09-05</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
         <v>130400</v>
       </c>
@@ -1816,7 +1791,6 @@
           <t>2022-06-03</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
         <v>104800</v>
       </c>
@@ -1868,7 +1842,6 @@
           <t>2024-03-24</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
         <v>125700</v>
       </c>
@@ -1920,7 +1893,6 @@
           <t>2023-01-02</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
         <v>131000</v>
       </c>
@@ -1972,7 +1944,6 @@
           <t>2023-10-13</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
         <v>118300</v>
       </c>
@@ -2024,7 +1995,6 @@
           <t>2023-11-26</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
         <v>99500</v>
       </c>
@@ -2076,7 +2046,6 @@
           <t>2024-08-06</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
         <v>101000</v>
       </c>
@@ -2128,7 +2097,6 @@
           <t>2022-03-03</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
         <v>90800</v>
       </c>
@@ -2180,7 +2148,6 @@
           <t>2021-11-01</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
         <v>87900</v>
       </c>
@@ -2232,7 +2199,6 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
         <v>88200</v>
       </c>
@@ -2284,7 +2250,6 @@
           <t>2025-07-04</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
         <v>102000</v>
       </c>
@@ -2336,7 +2301,6 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
         <v>127400</v>
       </c>
@@ -2388,7 +2352,6 @@
           <t>2021-03-12</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
         <v>108400</v>
       </c>
@@ -2440,7 +2403,6 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
         <v>132200</v>
       </c>
@@ -2492,7 +2454,6 @@
           <t>2022-03-15</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
         <v>127600</v>
       </c>
@@ -2544,7 +2505,6 @@
           <t>2026-01-12</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
         <v>78500</v>
       </c>
@@ -2596,7 +2556,6 @@
           <t>2019-08-26</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
         <v>74800</v>
       </c>
@@ -2648,7 +2607,6 @@
           <t>2019-05-13</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
         <v>183100</v>
       </c>
@@ -2700,7 +2658,6 @@
           <t>2019-07-02</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
         <v>101600</v>
       </c>
@@ -2752,7 +2709,6 @@
           <t>2021-02-08</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
         <v>172300</v>
       </c>
@@ -2804,7 +2760,6 @@
           <t>2024-12-23</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
         <v>126800</v>
       </c>
@@ -2856,7 +2811,6 @@
           <t>2022-04-27</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
         <v>145000</v>
       </c>
@@ -2908,7 +2862,6 @@
           <t>2024-05-06</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
         <v>124100</v>
       </c>
@@ -2960,7 +2913,6 @@
           <t>2022-09-11</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
         <v>105000</v>
       </c>
@@ -3012,7 +2964,6 @@
           <t>2022-10-19</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
         <v>126900</v>
       </c>
@@ -3064,7 +3015,6 @@
           <t>2023-07-10</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
         <v>94100</v>
       </c>
@@ -3116,7 +3066,6 @@
           <t>2022-04-05</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
         <v>122200</v>
       </c>
@@ -3168,7 +3117,6 @@
           <t>2023-03-12</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
         <v>99200</v>
       </c>
@@ -3220,7 +3168,6 @@
           <t>2024-08-23</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
         <v>108500</v>
       </c>
@@ -3272,7 +3219,6 @@
           <t>2019-05-08</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
         <v>110600</v>
       </c>
@@ -3324,7 +3270,6 @@
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
         <v>100300</v>
       </c>
@@ -3376,7 +3321,6 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
         <v>143600</v>
       </c>
@@ -3428,7 +3372,6 @@
           <t>2018-06-27</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
       <c r="G58" t="n">
         <v>111400</v>
       </c>
@@ -3480,7 +3423,6 @@
           <t>2022-01-09</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
         <v>139500</v>
       </c>
@@ -3532,7 +3474,6 @@
           <t>2019-01-15</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
         <v>121200</v>
       </c>
@@ -3584,7 +3525,6 @@
           <t>2022-12-14</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
         <v>109500</v>
       </c>
@@ -3636,7 +3576,6 @@
           <t>2023-09-05</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
         <v>125500</v>
       </c>
@@ -3688,7 +3627,6 @@
           <t>2019-05-02</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
         <v>121000</v>
       </c>
@@ -3740,7 +3678,6 @@
           <t>2025-05-09</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
         <v>115600</v>
       </c>
@@ -3792,7 +3729,6 @@
           <t>2022-09-06</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
         <v>155900</v>
       </c>
@@ -3844,7 +3780,6 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
         <v>76200</v>
       </c>
@@ -3896,7 +3831,6 @@
           <t>2022-11-26</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
         <v>153600</v>
       </c>
@@ -3948,7 +3882,6 @@
           <t>2022-05-26</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
         <v>161000</v>
       </c>
@@ -4000,7 +3933,6 @@
           <t>2025-09-05</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
       <c r="G69" t="n">
         <v>129600</v>
       </c>
@@ -4052,7 +3984,6 @@
           <t>2022-05-03</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
       <c r="G70" t="n">
         <v>107900</v>
       </c>
@@ -4104,7 +4035,6 @@
           <t>2025-01-24</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
         <v>94600</v>
       </c>
@@ -4156,7 +4086,6 @@
           <t>2024-10-22</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
       <c r="G72" t="n">
         <v>104600</v>
       </c>
@@ -4208,7 +4137,6 @@
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
         <v>108300</v>
       </c>
@@ -4260,7 +4188,6 @@
           <t>2018-07-03</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
         <v>145400</v>
       </c>
@@ -4312,7 +4239,6 @@
           <t>2022-01-07</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
         <v>125300</v>
       </c>
@@ -4364,7 +4290,6 @@
           <t>2025-04-27</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
         <v>77400</v>
       </c>
@@ -4416,7 +4341,6 @@
           <t>2022-12-18</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
         <v>106500</v>
       </c>
@@ -4468,7 +4392,6 @@
           <t>2024-11-02</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
         <v>120100</v>
       </c>
@@ -4520,7 +4443,6 @@
           <t>2022-08-21</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
         <v>114200</v>
       </c>
@@ -4572,7 +4494,6 @@
           <t>2021-11-26</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
         <v>119900</v>
       </c>
@@ -4624,7 +4545,6 @@
           <t>2022-06-15</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
         <v>117700</v>
       </c>
@@ -4676,7 +4596,6 @@
           <t>2023-10-07</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
         <v>103400</v>
       </c>
@@ -4728,7 +4647,6 @@
           <t>2023-08-12</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
         <v>110900</v>
       </c>
@@ -4780,7 +4698,6 @@
           <t>2019-06-19</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
       <c r="G84" t="n">
         <v>124100</v>
       </c>
@@ -4832,7 +4749,6 @@
           <t>2023-02-21</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
       <c r="G85" t="n">
         <v>89600</v>
       </c>
@@ -4884,7 +4800,6 @@
           <t>2022-02-13</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
       <c r="G86" t="n">
         <v>109100</v>
       </c>
@@ -4936,7 +4851,6 @@
           <t>2022-11-09</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
       <c r="G87" t="n">
         <v>114800</v>
       </c>
@@ -4988,7 +4902,6 @@
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
       <c r="G88" t="n">
         <v>124400</v>
       </c>
@@ -5040,7 +4953,6 @@
           <t>2024-07-28</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
       <c r="G89" t="n">
         <v>103500</v>
       </c>
@@ -5092,7 +5004,6 @@
           <t>2022-04-15</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
       <c r="G90" t="n">
         <v>98500</v>
       </c>
@@ -5144,7 +5055,6 @@
           <t>2019-02-05</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
         <v>156900</v>
       </c>
@@ -5196,7 +5106,6 @@
           <t>2019-12-03</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
         <v>133000</v>
       </c>
@@ -5248,7 +5157,6 @@
           <t>2025-09-26</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
       <c r="G93" t="n">
         <v>112400</v>
       </c>
@@ -5300,7 +5208,6 @@
           <t>2025-07-19</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
       <c r="G94" t="n">
         <v>107200</v>
       </c>
@@ -5352,7 +5259,6 @@
           <t>2023-09-06</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr"/>
       <c r="G95" t="n">
         <v>165400</v>
       </c>
@@ -5404,7 +5310,6 @@
           <t>2021-08-24</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
         <v>113900</v>
       </c>
@@ -5456,7 +5361,6 @@
           <t>2023-10-13</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
         <v>98200</v>
       </c>
@@ -5508,7 +5412,6 @@
           <t>2023-11-25</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr"/>
       <c r="G98" t="n">
         <v>108000</v>
       </c>
@@ -5560,7 +5463,6 @@
           <t>2021-12-27</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr"/>
       <c r="G99" t="n">
         <v>89500</v>
       </c>
@@ -5612,7 +5514,6 @@
           <t>2019-07-17</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr"/>
       <c r="G100" t="n">
         <v>126200</v>
       </c>
@@ -5664,7 +5565,6 @@
           <t>2022-09-12</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr"/>
       <c r="G101" t="n">
         <v>133600</v>
       </c>
@@ -5716,7 +5616,6 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
       <c r="G102" t="n">
         <v>99600</v>
       </c>
@@ -5768,7 +5667,6 @@
           <t>2019-02-20</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr"/>
       <c r="G103" t="n">
         <v>113300</v>
       </c>
@@ -5820,7 +5718,6 @@
           <t>2023-01-13</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
       <c r="G104" t="n">
         <v>100700</v>
       </c>
@@ -5872,7 +5769,6 @@
           <t>2022-06-24</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
       <c r="G105" t="n">
         <v>175600</v>
       </c>
@@ -5924,7 +5820,6 @@
           <t>2024-09-04</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr"/>
       <c r="G106" t="n">
         <v>103800</v>
       </c>
@@ -5976,7 +5871,6 @@
           <t>2025-02-17</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr"/>
       <c r="G107" t="n">
         <v>121600</v>
       </c>
@@ -6028,7 +5922,6 @@
           <t>2023-02-11</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr"/>
       <c r="G108" t="n">
         <v>130500</v>
       </c>
@@ -6080,7 +5973,6 @@
           <t>2022-08-23</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr"/>
       <c r="G109" t="n">
         <v>94700</v>
       </c>
@@ -6132,7 +6024,6 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr"/>
       <c r="G110" t="n">
         <v>100000</v>
       </c>
@@ -6184,7 +6075,6 @@
           <t>2018-04-26</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr"/>
       <c r="G111" t="n">
         <v>97700</v>
       </c>
@@ -6236,7 +6126,6 @@
           <t>2023-02-22</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr"/>
       <c r="G112" t="n">
         <v>116000</v>
       </c>
@@ -6288,7 +6177,6 @@
           <t>2024-09-04</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr"/>
       <c r="G113" t="n">
         <v>143200</v>
       </c>
@@ -6340,7 +6228,6 @@
           <t>2022-12-14</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr"/>
       <c r="G114" t="n">
         <v>174400</v>
       </c>
@@ -6392,7 +6279,6 @@
           <t>2018-12-14</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr"/>
       <c r="G115" t="n">
         <v>144300</v>
       </c>
@@ -6444,7 +6330,6 @@
           <t>2024-02-24</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr"/>
       <c r="G116" t="n">
         <v>137000</v>
       </c>
@@ -6496,7 +6381,6 @@
           <t>2025-01-22</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr"/>
       <c r="G117" t="n">
         <v>142700</v>
       </c>
@@ -6548,7 +6432,6 @@
           <t>2022-09-26</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
         <v>115000</v>
       </c>
@@ -6600,7 +6483,6 @@
           <t>2024-01-15</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr"/>
       <c r="G119" t="n">
         <v>89200</v>
       </c>
@@ -6652,7 +6534,6 @@
           <t>2024-06-20</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr"/>
       <c r="G120" t="n">
         <v>82400</v>
       </c>
@@ -6704,7 +6585,6 @@
           <t>2024-07-21</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
         <v>111300</v>
       </c>
@@ -6756,7 +6636,6 @@
           <t>2020-06-01</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr"/>
       <c r="G122" t="n">
         <v>98300</v>
       </c>
@@ -6808,7 +6687,6 @@
           <t>2023-10-21</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr"/>
       <c r="G123" t="n">
         <v>116400</v>
       </c>
@@ -6860,7 +6738,6 @@
           <t>2022-04-08</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr"/>
       <c r="G124" t="n">
         <v>115300</v>
       </c>
@@ -6912,7 +6789,6 @@
           <t>2023-10-13</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr"/>
       <c r="G125" t="n">
         <v>87200</v>
       </c>
@@ -6964,7 +6840,6 @@
           <t>2022-07-12</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr"/>
       <c r="G126" t="n">
         <v>102600</v>
       </c>
@@ -7016,7 +6891,6 @@
           <t>2024-11-21</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr"/>
       <c r="G127" t="n">
         <v>93300</v>
       </c>
@@ -7068,7 +6942,6 @@
           <t>2021-07-23</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr"/>
       <c r="G128" t="n">
         <v>111200</v>
       </c>
@@ -7120,7 +6993,6 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr"/>
       <c r="G129" t="n">
         <v>86800</v>
       </c>
@@ -7172,7 +7044,6 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr"/>
       <c r="G130" t="n">
         <v>105200</v>
       </c>
@@ -7224,7 +7095,6 @@
           <t>2023-03-07</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr"/>
       <c r="G131" t="n">
         <v>121500</v>
       </c>
@@ -7276,7 +7146,6 @@
           <t>2021-03-24</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr"/>
       <c r="G132" t="n">
         <v>108600</v>
       </c>
@@ -7328,7 +7197,6 @@
           <t>2023-09-22</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr"/>
       <c r="G133" t="n">
         <v>165800</v>
       </c>
@@ -7380,7 +7248,6 @@
           <t>2023-01-27</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr"/>
       <c r="G134" t="n">
         <v>111200</v>
       </c>
@@ -7432,7 +7299,6 @@
           <t>2024-05-18</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr"/>
       <c r="G135" t="n">
         <v>100300</v>
       </c>
@@ -7484,7 +7350,6 @@
           <t>2023-12-17</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr"/>
       <c r="G136" t="n">
         <v>122400</v>
       </c>
@@ -7536,7 +7401,6 @@
           <t>2021-11-19</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr"/>
       <c r="G137" t="n">
         <v>168200</v>
       </c>
@@ -7588,7 +7452,6 @@
           <t>2018-04-19</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr"/>
       <c r="G138" t="n">
         <v>155600</v>
       </c>
@@ -7640,7 +7503,6 @@
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr"/>
       <c r="G139" t="n">
         <v>116800</v>
       </c>
@@ -7692,7 +7554,6 @@
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr"/>
       <c r="G140" t="n">
         <v>100300</v>
       </c>
@@ -7744,7 +7605,6 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr"/>
       <c r="G141" t="n">
         <v>117000</v>
       </c>
@@ -7796,7 +7656,6 @@
           <t>2024-02-28</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr"/>
       <c r="G142" t="n">
         <v>103200</v>
       </c>
@@ -7848,7 +7707,6 @@
           <t>2021-07-04</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr"/>
       <c r="G143" t="n">
         <v>176800</v>
       </c>
@@ -7900,7 +7758,6 @@
           <t>2021-01-15</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr"/>
       <c r="G144" t="n">
         <v>152100</v>
       </c>
@@ -7952,7 +7809,6 @@
           <t>2022-04-10</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr"/>
       <c r="G145" t="n">
         <v>149200</v>
       </c>
@@ -8004,7 +7860,6 @@
           <t>2024-03-21</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr"/>
       <c r="G146" t="n">
         <v>162000</v>
       </c>
@@ -8056,7 +7911,6 @@
           <t>2022-09-18</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr"/>
       <c r="G147" t="n">
         <v>86900</v>
       </c>
@@ -8108,7 +7962,6 @@
           <t>2020-04-09</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr"/>
       <c r="G148" t="n">
         <v>121400</v>
       </c>
@@ -8160,7 +8013,6 @@
           <t>2023-12-16</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr"/>
       <c r="G149" t="n">
         <v>109500</v>
       </c>
@@ -8212,7 +8064,6 @@
           <t>2024-07-22</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr"/>
       <c r="G150" t="n">
         <v>102100</v>
       </c>
@@ -8264,7 +8115,6 @@
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr"/>
       <c r="G151" t="n">
         <v>115300</v>
       </c>
@@ -8316,7 +8166,6 @@
           <t>2024-03-01</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr"/>
       <c r="G152" t="n">
         <v>110500</v>
       </c>
@@ -8368,7 +8217,6 @@
           <t>2022-11-06</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr"/>
       <c r="G153" t="n">
         <v>152700</v>
       </c>
@@ -8420,7 +8268,6 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr"/>
       <c r="G154" t="n">
         <v>116000</v>
       </c>
@@ -8472,7 +8319,6 @@
           <t>2024-01-12</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr"/>
       <c r="G155" t="n">
         <v>101100</v>
       </c>
@@ -8524,7 +8370,6 @@
           <t>2022-05-19</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr"/>
       <c r="G156" t="n">
         <v>105000</v>
       </c>
@@ -8642,7 +8487,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I158" t="n">
@@ -8698,7 +8543,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I159" t="n">
@@ -8866,7 +8711,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I162" t="n">
@@ -8922,7 +8767,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I163" t="n">
@@ -9146,7 +8991,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I167" t="n">
@@ -9202,7 +9047,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I168" t="n">
@@ -9314,7 +9159,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I170" t="n">
@@ -9370,7 +9215,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I171" t="n">
@@ -9472,7 +9317,6 @@
           <t>2019-04-28</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr"/>
       <c r="G173" t="n">
         <v>145600</v>
       </c>
@@ -9590,7 +9434,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I175" t="n">
@@ -9646,7 +9490,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I176" t="n">
@@ -9758,7 +9602,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I178" t="n">
@@ -9982,7 +9826,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I182" t="n">
@@ -10038,7 +9882,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I183" t="n">
@@ -10206,7 +10050,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I186" t="n">
@@ -10374,7 +10218,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I189" t="n">
@@ -10486,7 +10330,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I191" t="n">
@@ -10542,7 +10386,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I192" t="n">
@@ -11046,7 +10890,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I201" t="n">
@@ -11382,7 +11226,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I207" t="n">
@@ -11886,7 +11730,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I216" t="n">
@@ -12110,7 +11954,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I220" t="n">
@@ -12222,7 +12066,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I222" t="n">
@@ -12278,7 +12122,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I223" t="n">
@@ -12390,7 +12234,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I225" t="n">
@@ -12446,7 +12290,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I226" t="n">
@@ -12502,7 +12346,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I227" t="n">
@@ -12670,7 +12514,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I230" t="n">
@@ -12838,7 +12682,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I233" t="n">
@@ -12894,7 +12738,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I234" t="n">
@@ -12950,7 +12794,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I235" t="n">
@@ -13230,7 +13074,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I240" t="n">
@@ -13276,7 +13120,6 @@
           <t>2024-07-21</t>
         </is>
       </c>
-      <c r="F241" t="inlineStr"/>
       <c r="G241" t="n">
         <v>120700</v>
       </c>
@@ -13450,7 +13293,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I244" t="n">
@@ -13842,7 +13685,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I251" t="n">
@@ -13898,7 +13741,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I252" t="n">
@@ -13954,7 +13797,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I253" t="n">
@@ -14066,7 +13909,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I255" t="n">
@@ -14122,7 +13965,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I256" t="n">
@@ -14178,7 +14021,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I257" t="n">
@@ -14234,7 +14077,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I258" t="n">
@@ -14458,7 +14301,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I262" t="n">
@@ -14850,7 +14693,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I269" t="n">
@@ -15130,7 +14973,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I274" t="n">
@@ -15410,7 +15253,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I279" t="n">
@@ -15466,7 +15309,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I280" t="n">
@@ -15578,7 +15421,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I282" t="n">
@@ -15858,7 +15701,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I287" t="n">
@@ -16362,7 +16205,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I296" t="n">
@@ -16418,7 +16261,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I297" t="n">
@@ -16474,7 +16317,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I298" t="n">
@@ -16642,7 +16485,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I301" t="n">
@@ -16922,7 +16765,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I306" t="n">
@@ -16978,7 +16821,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I307" t="n">

--- a/documents/engineering.xlsx
+++ b/documents/engineering.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L307"/>
+  <dimension ref="A1:L324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,12 +567,17 @@
           <t>2024-08-27</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
       <c r="G3" t="n">
         <v>117400</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -873,12 +878,17 @@
           <t>2023-05-21</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="G9" t="n">
         <v>120800</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -924,12 +934,17 @@
           <t>2025-01-09</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
       <c r="G10" t="n">
         <v>140300</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -1077,12 +1092,17 @@
           <t>2018-03-14</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
       <c r="G13" t="n">
         <v>199600</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1179,12 +1199,17 @@
           <t>2022-12-15</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="G15" t="n">
         <v>137600</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1383,12 +1408,17 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
       <c r="G19" t="n">
         <v>115300</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1485,12 +1515,17 @@
           <t>2021-12-08</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
       <c r="G21" t="n">
         <v>120000</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -2454,12 +2489,17 @@
           <t>2022-03-15</t>
         </is>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="G40" t="n">
         <v>127600</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -2913,12 +2953,17 @@
           <t>2022-09-11</t>
         </is>
       </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
       <c r="G49" t="n">
         <v>105000</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -3678,12 +3723,17 @@
           <t>2025-05-09</t>
         </is>
       </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="G64" t="n">
         <v>115600</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I64" t="n">
@@ -4035,12 +4085,17 @@
           <t>2025-01-24</t>
         </is>
       </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
       <c r="G71" t="n">
         <v>94600</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I71" t="n">
@@ -4494,12 +4549,17 @@
           <t>2021-11-26</t>
         </is>
       </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
       <c r="G80" t="n">
         <v>119900</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -4749,12 +4809,17 @@
           <t>2023-02-21</t>
         </is>
       </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="G85" t="n">
         <v>89600</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I85" t="n">
@@ -4800,12 +4865,17 @@
           <t>2022-02-13</t>
         </is>
       </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
       <c r="G86" t="n">
         <v>109100</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I86" t="n">
@@ -5106,12 +5176,17 @@
           <t>2019-12-03</t>
         </is>
       </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="G92" t="n">
         <v>133000</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I92" t="n">
@@ -5208,12 +5283,17 @@
           <t>2025-07-19</t>
         </is>
       </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="G94" t="n">
         <v>107200</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I94" t="n">
@@ -5259,12 +5339,17 @@
           <t>2023-09-06</t>
         </is>
       </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
       <c r="G95" t="n">
         <v>165400</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I95" t="n">
@@ -5412,12 +5497,17 @@
           <t>2023-11-25</t>
         </is>
       </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
       <c r="G98" t="n">
         <v>108000</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I98" t="n">
@@ -5463,12 +5553,17 @@
           <t>2021-12-27</t>
         </is>
       </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
       <c r="G99" t="n">
         <v>89500</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I99" t="n">
@@ -5616,12 +5711,17 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
       <c r="G102" t="n">
         <v>99600</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I102" t="n">
@@ -6279,12 +6379,17 @@
           <t>2018-12-14</t>
         </is>
       </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="G115" t="n">
         <v>144300</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I115" t="n">
@@ -6687,12 +6792,17 @@
           <t>2023-10-21</t>
         </is>
       </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="G123" t="n">
         <v>116400</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I123" t="n">
@@ -7095,12 +7205,17 @@
           <t>2023-03-07</t>
         </is>
       </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
       <c r="G131" t="n">
         <v>121500</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I131" t="n">
@@ -7248,12 +7363,17 @@
           <t>2023-01-27</t>
         </is>
       </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="G134" t="n">
         <v>111200</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I134" t="n">
@@ -7299,12 +7419,17 @@
           <t>2024-05-18</t>
         </is>
       </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
       <c r="G135" t="n">
         <v>100300</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I135" t="n">
@@ -8166,12 +8291,17 @@
           <t>2024-03-01</t>
         </is>
       </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
       <c r="G152" t="n">
         <v>110500</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I152" t="n">
@@ -8217,12 +8347,17 @@
           <t>2022-11-06</t>
         </is>
       </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
       <c r="G153" t="n">
         <v>152700</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I153" t="n">
@@ -16836,6 +16971,873 @@
         </is>
       </c>
       <c r="L307" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Angela Perez</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>1986-06-16</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G308" t="n">
+        <v>98700</v>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I308" t="n">
+        <v>0</v>
+      </c>
+      <c r="J308" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>Asian</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Amanda Cooper</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>1988-06-27</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Engineering Manager</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G309" t="n">
+        <v>142300</v>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I309" t="n">
+        <v>1</v>
+      </c>
+      <c r="J309" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Pamela Rogers</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>1968-09-09</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Junior Engineer</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="G310" t="n">
+        <v>95600</v>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I310" t="n">
+        <v>2</v>
+      </c>
+      <c r="J310" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Janice Simmons</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>1994-03-06</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Junior Engineer</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="G311" t="n">
+        <v>75900</v>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I311" t="n">
+        <v>3</v>
+      </c>
+      <c r="J311" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Jose James</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>1973-06-04</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>VP Engineering</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G312" t="n">
+        <v>152300</v>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I312" t="n">
+        <v>0</v>
+      </c>
+      <c r="J312" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>Hispanic</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Timothy White</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>1995-10-25</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="G313" t="n">
+        <v>103000</v>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I313" t="n">
+        <v>1</v>
+      </c>
+      <c r="J313" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Kelly Miller</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>1997-05-26</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Lead Engineer</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G314" t="n">
+        <v>129300</v>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I314" t="n">
+        <v>3</v>
+      </c>
+      <c r="J314" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Carl Garcia</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>1976-06-03</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G315" t="n">
+        <v>134100</v>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I315" t="n">
+        <v>0</v>
+      </c>
+      <c r="J315" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>Hispanic</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Rachel Nguyen</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>1997-06-06</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G316" t="n">
+        <v>121300</v>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I316" t="n">
+        <v>1</v>
+      </c>
+      <c r="J316" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Nancy James</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>1976-08-16</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G317" t="n">
+        <v>122900</v>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I317" t="n">
+        <v>0</v>
+      </c>
+      <c r="J317" t="n">
+        <v>6</v>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Christopher Wright</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>1975-06-03</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="G318" t="n">
+        <v>93600</v>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I318" t="n">
+        <v>0</v>
+      </c>
+      <c r="J318" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>Asian</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Kyle Cooper</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>2003-06-18</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="G319" t="n">
+        <v>108800</v>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I319" t="n">
+        <v>2</v>
+      </c>
+      <c r="J319" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>James Wood</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>2002-03-08</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>VP Engineering</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="G320" t="n">
+        <v>159100</v>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I320" t="n">
+        <v>2</v>
+      </c>
+      <c r="J320" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>Hispanic</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Maria Fisher</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>2001-07-17</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G321" t="n">
+        <v>105300</v>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I321" t="n">
+        <v>2</v>
+      </c>
+      <c r="J321" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Rebecca Phillips</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>1993-10-06</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="G322" t="n">
+        <v>115700</v>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I322" t="n">
+        <v>0</v>
+      </c>
+      <c r="J322" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Kathleen Gonzalez</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>1979-04-01</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="G323" t="n">
+        <v>108000</v>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I323" t="n">
+        <v>1</v>
+      </c>
+      <c r="J323" t="n">
+        <v>1</v>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Roger King</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>1987-06-15</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="G324" t="n">
+        <v>104500</v>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I324" t="n">
+        <v>2</v>
+      </c>
+      <c r="J324" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
         <is>
           <t>White</t>
         </is>
